--- a/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
+++ b/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\存档表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D6D1F-1D69-4C51-86EE-2E9D73811E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7CA4F6-FB5D-4AD8-B784-5460B3B5DAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="东亚强冷站" sheetId="3" r:id="rId1"/>
-    <sheet name="日温阈值天数对比" sheetId="4" r:id="rId2"/>
+    <sheet name="夜温阈值" sheetId="4" r:id="rId2"/>
+    <sheet name="昼温阈值" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="201">
   <si>
     <t>地点</t>
   </si>
@@ -681,104 +682,302 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>地点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>尤里卡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>非定居点</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>塔吉克斯坦 山地巴达赫尚自治州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>青藏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>东北</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>沱沱河</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SAJMAK</t>
+    <t>查干诺尔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="24"/>
-        <color rgb="FFFFAC00"/>
+        <sz val="22"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <color rgb="FFFFC000"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="134"/>
         <scheme val="major"/>
       </rPr>
-      <t>分区</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>-40°C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天数</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Tomtor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1952-1953冬
+1972-1973冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFAC00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">海拔
-</t>
+      <t>1966</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
-        <color rgb="FFFFAC00"/>
-        <rFont val="Arial"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <charset val="134"/>
       </rPr>
-      <t>(m)</t>
+      <t>冬</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFAC00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>纬度</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFAC00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">
-(°)</t>
-    </r>
+    <t>1957-1958冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Toko</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1965-1966冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+萨哈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿拉卡基特</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1970-1971冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国
+阿拉斯加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allakaket</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	1968-1969冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+外贝加尔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中卡拉尔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Средний Калар</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Томтор
+奥伊米亚康区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1968-1969冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>东戈壁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古
+乌布苏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大
+努纳武特</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Зүүнговь</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古
+呼伦贝尔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞典
+北博滕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>青海
+海西</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plateau Station</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高原站(美国)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1985-1986冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根河</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+图瓦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>克孜勒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1944-1945冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡拉绍克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1916-1917冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>挪威
+芬马克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kárášjohka</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vuoggatjålme</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1903-1904冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pokegama Dam</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vuoggatjalme</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国(本土)
+明尼苏达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+克拉斯诺亚尔斯克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿加塔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Агата</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+伊尔库茨克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纳坎诺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Наканно</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1935-1936冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>科什阿加奇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+阿尔泰共和国</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Кош-Агач</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Кызыл</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -786,341 +985,47 @@
       <rPr>
         <sz val="12"/>
         <color theme="2" tint="-0.34998626667073579"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
+        <charset val="204"/>
       </rPr>
-      <t>非定居点</t>
+      <t>Токо</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="2" tint="-0.34998626667073579"/>
-        <rFont val="Arial"/>
+        <rFont val="微软雅黑"/>
         <family val="2"/>
-        <scheme val="major"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>南半球</t>
+外兴安岭 废弃机场</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>尼卡卢奥克塔</t>
-    </r>
+    <t>🌏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>🪪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>苏福尔斯</t>
+      <t>2004-2005</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="10"/>
+        <sz val="15"/>
         <color rgb="FFFFFF00"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>格陵兰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>冰盖高原</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>西伯利亚</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>外兴安岭</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>南西伯利亚中部</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">南西伯利亚东部
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>贝加尔湖以东</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>南极</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>冰盖高原</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>加拿大</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>西北</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>蒙古国</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>哈萨克斯坦</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>美国本土</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>吉尔吉斯斯坦</t>
+      <t>冬</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1128,7 +1033,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="0"/>
+        <color theme="4" tint="0.39997558519241921"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="134"/>
@@ -1140,246 +1045,65 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>青海</t>
+      <t xml:space="preserve">单个冬季 </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <b/>
+        <sz val="48"/>
         <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-40°C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="48"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <b/>
+        <sz val="48"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
-        <scheme val="major"/>
       </rPr>
-      <t>海西蒙古族藏族自治州</t>
+      <t>天数</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>美国</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>阿拉斯加</t>
-    </r>
+    <t>Lake Hazen</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="13"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
+        <sz val="20"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">高原穹顶
-</t>
+      <t>昼温</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="13"/>
+        <sz val="20"/>
         <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>EAGLE</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>顶峰营</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>上扬斯克</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>博代博</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>丹麦
-格陵兰自治区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>俄罗斯
-萨哈共和国</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>加拿大
-努纳武特地区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>俄罗斯
-伊尔库茨克州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>美国
-阿拉斯加州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑞典
-北博滕省</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>美国
-南达科他州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>俄罗斯
-后贝加尔边疆区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IMENI
-ODINNADTSATOGO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>仁钦隆勃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蒙古
-库苏古尔省</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>卡丘格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑龙江
-大兴安岭地区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>呼玛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古
-呼伦贝尔地区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>海拉尔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OLIKTOK
-POW 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAINWRIGHT
-LIZ 3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>巴音布鲁克</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新疆 巴音郭楞蒙古自治州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈萨克斯坦
-巴甫洛达尔州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>巴甫洛达尔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>塔吉克斯坦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>穆尔加布</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>北欧三国</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>苏萨梅尔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吉尔吉斯斯坦
-楚河州</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单个冬季</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>整日低于</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="微软雅黑"/>
+        <rFont val="宋体"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -1388,487 +1112,49 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="20"/>
         <color theme="0"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>-30</t>
+      <t xml:space="preserve">-30°C </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="1"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
+        <sz val="20"/>
         <color rgb="FFFFC000"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>最多天数</t>
+      <t>天数</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>( 2019/2020</t>
+      <t xml:space="preserve">单个冬季 </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="15"/>
+        <sz val="32"/>
         <color theme="0"/>
-        <rFont val="Arial"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
-        <scheme val="major"/>
       </rPr>
-      <t>冬</t>
+      <t>昼温低于-30°C</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 2000/2001</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
+        <sz val="32"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
         <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1956/1957</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1968/1969</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1964/1965</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1949/1950</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 2009/2010</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1983/1984</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 2016/2017</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 2011/2012</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1960/1961</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1986/1987</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1995/1996</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1985/1986</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>( 1977/1978</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>冬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>各地区 单个冬季</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1876,88 +1162,14 @@
     <r>
       <rPr>
         <b/>
-        <sz val="28"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">整日低于 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>-30</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="1"/>
-      </rPr>
-      <t>℃</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
-        <color theme="0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="28"/>
+        <sz val="32"/>
         <color rgb="FF00B0F0"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">最多天数
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="2" tint="-0.249977111117893"/>
-        <rFont val="黑体"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>数据统一来自NOAA逐日档案，国内缺失68-69大冷冬资料(北极村25次昼温低于-30)</t>
+      <t>最多天数</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>北极村</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>查干诺尔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1969,9 +1181,9 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-m"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="78" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1982,6 +1194,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2210,140 +1423,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFF00"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFC000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FFFFAC00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FFFFAC00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFC000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFC000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFAC00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFAC00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFAC00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="major"/>
@@ -2364,84 +1445,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFC000"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFF00"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="0"/>
@@ -2458,34 +1461,10 @@
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color theme="2" tint="-0.249977111117893"/>
       <name val="Arial"/>
       <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -2497,90 +1476,11 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF00B0F0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color theme="0"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="28"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -2599,8 +1499,255 @@
     </font>
     <font>
       <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFAC00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFC000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFAC00"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFFAC00"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF92D050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FF00B0F0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF92D050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFC000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFC000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2608,22 +1755,30 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color theme="2" tint="-0.249977111117893"/>
-      <name val="黑体"/>
+      <sz val="32"/>
+      <color rgb="FF00B0F0"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="32"/>
       <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2780,6 +1935,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF560BAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -2855,19 +2016,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="0"/>
-      </left>
-      <right style="medium">
-        <color theme="0"/>
-      </right>
-      <top style="medium">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color theme="0"/>
       </left>
@@ -2877,19 +2025,6 @@
       <top style="double">
         <color theme="0"/>
       </top>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color theme="0"/>
-      </left>
-      <right style="double">
-        <color theme="0"/>
-      </right>
-      <top/>
       <bottom style="double">
         <color theme="0"/>
       </bottom>
@@ -2916,23 +2051,47 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="medium">
         <color theme="0"/>
       </left>
-      <right style="double">
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="double">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="double">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color theme="0"/>
       </right>
-      <top style="double">
+      <top style="medium">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="double">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3054,7 +2213,7 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3069,187 +2228,161 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="58" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="59" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="41" fillId="17" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="19" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="20" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="21" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="24" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="41" fillId="25" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="41" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="58" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="59" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="61" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="53" fillId="23" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="54" fillId="20" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="54" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="17" fontId="54" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="58" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="58" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="17" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="80" fillId="17" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="18" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="19" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="19" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="20" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="20" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="21" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="21" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="23" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="24" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="61" fillId="24" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="25" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="80" fillId="25" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="80" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3279,32 +2412,32 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="35" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3314,16 +2447,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF4895EF"/>
+      <color rgb="FFF72585"/>
       <color rgb="FF4CC9F0"/>
-      <color rgb="FF4895EF"/>
       <color rgb="FF4361EE"/>
       <color rgb="FF3F37C9"/>
       <color rgb="FF3A0CA3"/>
       <color rgb="FF480CA8"/>
+      <color rgb="FF560BAD"/>
       <color rgb="FF7209B7"/>
       <color rgb="FFB5179E"/>
-      <color rgb="FFF72585"/>
-      <color rgb="FF560BAD"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3556,21 +2689,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="112"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="104"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -3587,35 +2720,35 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="107" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="115" t="s">
+      <c r="C2" s="107" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="113" t="s">
+      <c r="D2" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="113" t="s">
+      <c r="E2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="118" t="s">
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="110" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="109"/>
-      <c r="J2" s="108" t="s">
+      <c r="I2" s="101"/>
+      <c r="J2" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="K2" s="109"/>
-      <c r="L2" s="108" t="s">
+      <c r="K2" s="101"/>
+      <c r="L2" s="100" t="s">
         <v>131</v>
       </c>
-      <c r="M2" s="109"/>
+      <c r="M2" s="101"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -3632,13 +2765,13 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="116"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
       <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
@@ -3946,8 +3079,8 @@
       <c r="F9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="107" t="s">
-        <v>216</v>
+      <c r="G9" s="60" t="s">
+        <v>139</v>
       </c>
       <c r="H9" s="29">
         <v>-33.299999999999997</v>
@@ -33399,570 +32532,469 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F386B1A-4DAD-4626-8EB7-CF08CB4064B1}">
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" style="49" customWidth="1"/>
-    <col min="2" max="2" width="14.59765625" style="47" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="47" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" style="47" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="50" customWidth="1"/>
-    <col min="6" max="6" width="8.59765625" style="48" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" style="48" customWidth="1"/>
-    <col min="8" max="8" width="9.59765625" style="47" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="47"/>
+    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" style="92" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="71" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="47" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="124" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-    </row>
-    <row r="2" spans="1:8" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="82" t="s">
+    <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="97" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99"/>
+    </row>
+    <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="94"/>
+      <c r="E2" s="75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="81" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="50">
+        <v>335</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="51">
+        <v>152</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="87" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="52">
+        <v>122</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="88" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="53">
+        <v>107</v>
+      </c>
+      <c r="D6" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="53">
+        <v>104</v>
+      </c>
+      <c r="D7" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="128" t="s">
+      <c r="E7" s="74" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="76">
+        <v>92</v>
+      </c>
+      <c r="D8" s="79" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="88" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="76">
+        <v>91</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="54">
+        <v>81</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="90" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="55">
+        <v>69</v>
+      </c>
+      <c r="D11" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="48"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="55">
+        <v>67</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" s="88" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="55">
+        <v>65</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="84" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="56">
+        <v>57</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="90" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="126" t="s">
-        <v>198</v>
-      </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="83" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="83" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="84"/>
-    </row>
-    <row r="3" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="79" t="s">
+      <c r="C15" s="57">
+        <v>37</v>
+      </c>
+      <c r="D15" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="86">
-        <v>356</v>
-      </c>
-      <c r="E3" s="87" t="s">
-        <v>207</v>
-      </c>
-      <c r="F3" s="80">
-        <v>2830</v>
-      </c>
-      <c r="G3" s="85">
-        <v>76.42</v>
-      </c>
-      <c r="H3" s="81" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="69" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="88">
-        <v>162</v>
-      </c>
-      <c r="E4" s="89" t="s">
+      <c r="E15" s="48"/>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="87" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="58">
+        <v>20</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="48"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="82" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="59">
+        <v>14</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="87" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="59">
+        <v>14</v>
+      </c>
+      <c r="D18" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="73" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E18">
+    <sortCondition descending="1" ref="C3:C18"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA111638-49D1-45ED-AEC5-4053BA8905D8}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
+  <cols>
+    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" style="92" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="71" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="47" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="118" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="120"/>
+    </row>
+    <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="96"/>
+      <c r="C2" s="113" t="s">
         <v>199</v>
       </c>
-      <c r="F4" s="52">
-        <v>3207</v>
-      </c>
-      <c r="G4" s="54">
-        <v>72.583333300000007</v>
-      </c>
-      <c r="H4" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="90">
-        <v>123</v>
-      </c>
-      <c r="E5" s="91" t="s">
-        <v>200</v>
-      </c>
-      <c r="F5" s="52">
-        <v>138</v>
-      </c>
-      <c r="G5" s="54">
-        <v>67.566666600000005</v>
-      </c>
-      <c r="H5" s="55"/>
-    </row>
-    <row r="6" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="71" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="92">
-        <v>118</v>
-      </c>
-      <c r="E6" s="93" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="52">
-        <v>10</v>
-      </c>
-      <c r="G6" s="53">
-        <v>79.983333299999998</v>
-      </c>
-      <c r="H6" s="55"/>
-    </row>
-    <row r="7" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="70" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="94">
-        <v>68</v>
-      </c>
-      <c r="E7" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="F7" s="52">
-        <v>278</v>
-      </c>
-      <c r="G7" s="54">
-        <v>57.85</v>
-      </c>
-      <c r="H7" s="55"/>
-    </row>
-    <row r="8" spans="1:8" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="120" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="94">
-        <v>64</v>
-      </c>
-      <c r="E8" s="95" t="s">
-        <v>203</v>
-      </c>
-      <c r="F8" s="56">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G8" s="54">
-        <v>70.5</v>
-      </c>
-      <c r="H8" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="121"/>
-      <c r="B9" s="68" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="94">
-        <v>64</v>
-      </c>
-      <c r="E9" s="95" t="s">
-        <v>203</v>
-      </c>
-      <c r="F9" s="52">
-        <v>27.1</v>
-      </c>
-      <c r="G9" s="54">
-        <v>70.616669999999999</v>
-      </c>
-      <c r="H9" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="72" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" s="96">
-        <v>50</v>
-      </c>
-      <c r="E10" s="97" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" s="52">
-        <v>1080</v>
-      </c>
-      <c r="G10" s="54">
-        <v>55.9</v>
-      </c>
-      <c r="H10" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="98">
-        <v>47</v>
-      </c>
-      <c r="E11" s="99" t="s">
-        <v>205</v>
-      </c>
-      <c r="F11" s="52">
-        <v>1583</v>
-      </c>
-      <c r="G11" s="54">
-        <v>51.116666600000002</v>
-      </c>
-      <c r="H11" s="55"/>
-    </row>
-    <row r="12" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="70" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="98">
-        <v>43</v>
-      </c>
-      <c r="E12" s="99" t="s">
-        <v>202</v>
-      </c>
-      <c r="F12" s="52">
-        <v>533</v>
-      </c>
-      <c r="G12" s="54">
-        <v>53.966666600000003</v>
-      </c>
-      <c r="H12" s="55"/>
-    </row>
-    <row r="13" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="74" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="100">
-        <v>22</v>
-      </c>
-      <c r="E13" s="101" t="s">
-        <v>202</v>
-      </c>
-      <c r="F13" s="52">
-        <v>124.96</v>
-      </c>
-      <c r="G13" s="54">
-        <v>52.195</v>
-      </c>
-      <c r="H13" s="55"/>
-    </row>
-    <row r="14" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="71" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="100">
-        <v>21</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="52">
-        <v>2459.1</v>
-      </c>
-      <c r="G14" s="54">
-        <v>43.0336</v>
-      </c>
-      <c r="H14" s="55"/>
-    </row>
-    <row r="15" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="122" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="68" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="D15" s="102">
-        <v>13</v>
-      </c>
-      <c r="E15" s="103" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="52">
-        <v>649.70000000000005</v>
-      </c>
-      <c r="G15" s="54">
-        <v>49.25</v>
-      </c>
-      <c r="H15" s="55"/>
-    </row>
-    <row r="16" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="122"/>
-      <c r="B16" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="102">
-        <v>13</v>
-      </c>
-      <c r="E16" s="103" t="s">
-        <v>209</v>
-      </c>
-      <c r="F16" s="52">
-        <v>173.9</v>
-      </c>
-      <c r="G16" s="54">
-        <v>51.733333299999998</v>
-      </c>
-      <c r="H16" s="55"/>
-    </row>
-    <row r="17" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="122"/>
-      <c r="B17" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="106" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="102">
-        <v>13</v>
-      </c>
-      <c r="E17" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="F17" s="52">
-        <v>433.9</v>
-      </c>
-      <c r="G17" s="54">
-        <v>52.974400000000003</v>
-      </c>
-      <c r="H17" s="55"/>
-    </row>
-    <row r="18" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="73" t="s">
-        <v>195</v>
-      </c>
-      <c r="B18" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="102">
-        <v>13</v>
-      </c>
-      <c r="E18" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="F18" s="52">
-        <v>468</v>
-      </c>
-      <c r="G18" s="54">
-        <v>67.849999999999994</v>
-      </c>
-      <c r="H18" s="55"/>
-    </row>
-    <row r="19" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="68" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="D19" s="102">
-        <v>10</v>
-      </c>
-      <c r="E19" s="103" t="s">
-        <v>211</v>
-      </c>
-      <c r="F19" s="52">
-        <v>481.52</v>
-      </c>
-      <c r="G19" s="54">
-        <v>43.733333299999998</v>
-      </c>
-      <c r="H19" s="55"/>
-    </row>
-    <row r="20" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="123" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="104">
-        <v>5</v>
-      </c>
-      <c r="E20" s="105" t="s">
-        <v>212</v>
-      </c>
-      <c r="F20" s="56">
-        <v>3840</v>
-      </c>
-      <c r="G20" s="53">
-        <v>37.533000000000001</v>
-      </c>
-      <c r="H20" s="55"/>
-    </row>
-    <row r="21" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="123"/>
-      <c r="B21" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="51" t="s">
+      <c r="D2" s="112"/>
+      <c r="E2" s="75" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="104">
-        <v>5</v>
-      </c>
-      <c r="E21" s="105" t="s">
-        <v>212</v>
-      </c>
-      <c r="F21" s="52">
-        <v>3576</v>
-      </c>
-      <c r="G21" s="54">
-        <v>38.166666599999999</v>
-      </c>
-      <c r="H21" s="55"/>
-    </row>
-    <row r="22" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="75" t="s">
-        <v>163</v>
-      </c>
-      <c r="B22" s="68" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D22" s="104">
-        <v>4</v>
-      </c>
-      <c r="E22" s="105" t="s">
-        <v>213</v>
-      </c>
-      <c r="F22" s="52">
-        <v>2092</v>
-      </c>
-      <c r="G22" s="54">
-        <v>42.15</v>
-      </c>
-      <c r="H22" s="66"/>
-    </row>
-    <row r="23" spans="1:8" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="76" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="67" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="56">
-        <v>4770</v>
-      </c>
-      <c r="G23" s="53">
-        <v>34.6</v>
-      </c>
-      <c r="H23" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="19.149999999999999" thickTop="1" x14ac:dyDescent="0.5"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="81"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="61"/>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="83"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="72"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="82"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="72"/>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="83"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="72"/>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="83"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="74"/>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="83"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="83"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="48"/>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="82"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="48"/>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="49"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="48"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="83"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="83"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="48"/>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="84"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="48"/>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="49"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="48"/>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="82"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="48"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="82"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="48"/>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="82"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="73"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H23">
-    <sortCondition descending="1" ref="D3:D23"/>
-    <sortCondition descending="1" ref="A3:A23"/>
-    <sortCondition ref="G3:G23"/>
-  </sortState>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B2:C2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
+++ b/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\存档表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E867AAD-F57C-497F-A7BA-654B752D5B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE16F2B-F6D3-44DE-8316-C92D5E29AB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="东亚强冷站" sheetId="3" r:id="rId1"/>
-    <sheet name="夜温阈值" sheetId="4" r:id="rId2"/>
-    <sheet name="连续夜温阈值" sheetId="5" r:id="rId3"/>
-    <sheet name="连续昼温阈值" sheetId="7" r:id="rId4"/>
+    <sheet name="东亚冷站9120一均" sheetId="3" r:id="rId1"/>
+    <sheet name="夜温-40阈值" sheetId="4" r:id="rId2"/>
+    <sheet name="昼温-30阈值" sheetId="8" r:id="rId3"/>
+    <sheet name="连续夜温-40阈值" sheetId="5" r:id="rId4"/>
+    <sheet name="连续昼温-30阈值" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="335">
   <si>
     <t>地点</t>
   </si>
@@ -2489,6 +2490,765 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">单个冬季 昼温低于 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="36"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-30°C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="36"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="36"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天数</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">单冬 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>昼温</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">&lt;= -30℃
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最多天数</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>南极</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1966</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>高原站</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>美国</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>俄罗斯
+萨哈</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Томтор
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="2" tint="-0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>奥伊米亚康区</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>加拿大
+努纳武特</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>尤里卡</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1971-1972</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>俄罗斯
+克拉斯诺亚尔斯克</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>俄罗斯
+伊尔库茨克</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>俄罗斯
+外贝加尔</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>美国
+阿拉斯加</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>内蒙古
+呼伦贝尔</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>俄罗斯
+图瓦</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>克孜勒</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>科什阿加奇</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>挪威
+芬马克</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>卡拉绍克</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌米阿特</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1989-1990</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Umiat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1965-1966</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1968-1969</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古
+库苏古尔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁钦隆勃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2009-2010</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ренчинлхүмбэ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆
+巴音郭楞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴音布鲁克</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1983-1984</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear Creek</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1915-1916</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>美国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>本土</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蒙大拿</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恰拉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Чара</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. 涅尔坎
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>2. Toko</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Нелькан
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="2" tint="-0.34998626667073579"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. 外兴安岭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="2" tint="-0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="2" tint="-0.34998626667073579"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>废弃机场</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>俄罗斯
+西伯利亚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>俄罗斯
+阿尔泰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1935-1936</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">冬
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>1946-1947冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1987-1988</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2000-2001</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2500,7 +3260,7 @@
     <numFmt numFmtId="178" formatCode="yyyy\-m"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="100">
+  <fonts count="115">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3270,6 +4030,125 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FF00B0F0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="28">
     <fill>
@@ -3584,7 +4463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3946,6 +4825,27 @@
     <xf numFmtId="0" fontId="81" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="97" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3961,10 +4861,10 @@
     <xf numFmtId="0" fontId="44" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="96" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4001,32 +4901,59 @@
     <xf numFmtId="0" fontId="47" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="35" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="27" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="106" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="113" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="114" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="111" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4278,21 +5205,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="80" customHeight="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="139" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="134"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="141"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -4309,35 +5236,35 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="48" customHeight="1">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="135" t="s">
+      <c r="D2" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="140" t="s">
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="147" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="131"/>
-      <c r="J2" s="130" t="s">
+      <c r="I2" s="138"/>
+      <c r="J2" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="K2" s="131"/>
-      <c r="L2" s="130" t="s">
+      <c r="K2" s="138"/>
+      <c r="L2" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="M2" s="131"/>
+      <c r="M2" s="138"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -4354,13 +5281,13 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="32" customHeight="1">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
+      <c r="A3" s="145"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
       <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
@@ -34133,23 +35060,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="130" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="133" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="142" t="s">
+      <c r="B2" s="134"/>
+      <c r="C2" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="143"/>
+      <c r="D2" s="150"/>
       <c r="E2" s="75" t="s">
         <v>194</v>
       </c>
@@ -34433,6 +35360,331 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867BCDEB-6279-47D1-8C43-6CA3B2BA5301}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="24.75"/>
+  <cols>
+    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" style="91" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="71" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="47" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1">
+      <c r="A1" s="153" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="155"/>
+    </row>
+    <row r="2" spans="1:5" ht="48" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" s="133" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="134"/>
+      <c r="C2" s="156" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="157"/>
+      <c r="E2" s="75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" thickTop="1">
+      <c r="A3" s="158" t="s">
+        <v>292</v>
+      </c>
+      <c r="B3" s="89" t="s">
+        <v>295</v>
+      </c>
+      <c r="C3" s="159">
+        <v>329</v>
+      </c>
+      <c r="D3" s="162" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="163" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1">
+      <c r="A4" s="158" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="159">
+        <v>125</v>
+      </c>
+      <c r="D4" s="162" t="s">
+        <v>334</v>
+      </c>
+      <c r="E4" s="163" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1">
+      <c r="A5" s="164" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="160">
+        <v>123</v>
+      </c>
+      <c r="D5" s="161" t="s">
+        <v>333</v>
+      </c>
+      <c r="E5" s="73" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1">
+      <c r="A6" s="164" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="160">
+        <v>127</v>
+      </c>
+      <c r="D6" s="161" t="s">
+        <v>300</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1">
+      <c r="A7" s="164" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="160">
+        <v>93</v>
+      </c>
+      <c r="D7" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1">
+      <c r="A8" s="49" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="166" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="160">
+        <v>66</v>
+      </c>
+      <c r="D8" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1">
+      <c r="A9" s="164" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="160">
+        <v>71</v>
+      </c>
+      <c r="D9" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1">
+      <c r="A10" s="164" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="97" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="160">
+        <v>61</v>
+      </c>
+      <c r="D10" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1">
+      <c r="A11" s="164" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="89" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11" s="160">
+        <v>71</v>
+      </c>
+      <c r="D11" s="161" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1">
+      <c r="A12" s="164" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="97" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="160"/>
+      <c r="D12" s="161" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1">
+      <c r="A13" s="164" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" s="89" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" s="160">
+        <v>41</v>
+      </c>
+      <c r="D13" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1">
+      <c r="A14" s="167" t="s">
+        <v>331</v>
+      </c>
+      <c r="B14" s="89" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="160">
+        <v>29</v>
+      </c>
+      <c r="D14" s="168" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1">
+      <c r="A15" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" s="97" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="160">
+        <v>43</v>
+      </c>
+      <c r="D15" s="161" t="s">
+        <v>318</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1">
+      <c r="A16" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="97" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="160">
+        <v>21</v>
+      </c>
+      <c r="D16" s="161" t="s">
+        <v>322</v>
+      </c>
+      <c r="E16" s="48"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1">
+      <c r="A17" s="165" t="s">
+        <v>325</v>
+      </c>
+      <c r="B17" s="89" t="s">
+        <v>323</v>
+      </c>
+      <c r="C17" s="160">
+        <v>9</v>
+      </c>
+      <c r="D17" s="161" t="s">
+        <v>324</v>
+      </c>
+      <c r="E17" s="48"/>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1">
+      <c r="A18" s="164" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" s="89" t="s">
+        <v>310</v>
+      </c>
+      <c r="C18" s="160">
+        <v>18</v>
+      </c>
+      <c r="D18" s="161" t="s">
+        <v>314</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="36" customHeight="1">
+      <c r="A19" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="89" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="160">
+        <v>25</v>
+      </c>
+      <c r="D19" s="161" t="s">
+        <v>315</v>
+      </c>
+      <c r="E19" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA111638-49D1-45ED-AEC5-4053BA8905D8}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="24.75"/>
@@ -34446,23 +35698,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="130" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="133" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="128" t="s">
+      <c r="B2" s="134"/>
+      <c r="C2" s="151" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="129"/>
+      <c r="D2" s="152"/>
       <c r="E2" s="75" t="s">
         <v>194</v>
       </c>
@@ -34766,7 +36018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F0BB6F-5228-4A30-866C-40DE5CC59526}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="24.75"/>
@@ -34780,23 +36032,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="130" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" ht="48" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="133" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="144" t="s">
+      <c r="B2" s="134"/>
+      <c r="C2" s="135" t="s">
         <v>262</v>
       </c>
-      <c r="D2" s="145"/>
+      <c r="D2" s="136"/>
       <c r="E2" s="75" t="s">
         <v>194</v>
       </c>
@@ -34814,7 +36066,7 @@
       <c r="D3" s="99" t="s">
         <v>258</v>
       </c>
-      <c r="E3" s="146" t="s">
+      <c r="E3" s="123" t="s">
         <v>260</v>
       </c>
     </row>
@@ -34876,10 +36128,10 @@
       <c r="B7" s="117" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="147">
+      <c r="C7" s="124">
         <v>49</v>
       </c>
-      <c r="D7" s="148" t="s">
+      <c r="D7" s="125" t="s">
         <v>256</v>
       </c>
       <c r="E7" s="94" t="s">
@@ -34893,10 +36145,10 @@
       <c r="B8" s="119" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="147">
+      <c r="C8" s="124">
         <v>42</v>
       </c>
-      <c r="D8" s="148" t="s">
+      <c r="D8" s="125" t="s">
         <v>269</v>
       </c>
       <c r="E8" s="72" t="s">
@@ -34907,13 +36159,13 @@
       <c r="A9" s="83" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="152" t="s">
+      <c r="B9" s="129" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="147">
+      <c r="C9" s="124">
         <v>42</v>
       </c>
-      <c r="D9" s="148" t="s">
+      <c r="D9" s="125" t="s">
         <v>268</v>
       </c>
       <c r="E9" s="94" t="s">
@@ -34927,10 +36179,10 @@
       <c r="B10" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="147">
+      <c r="C10" s="124">
         <v>40</v>
       </c>
-      <c r="D10" s="148" t="s">
+      <c r="D10" s="125" t="s">
         <v>257</v>
       </c>
       <c r="E10" s="94" t="s">
@@ -34944,10 +36196,10 @@
       <c r="B11" s="121" t="s">
         <v>286</v>
       </c>
-      <c r="C11" s="149">
+      <c r="C11" s="126">
         <v>38</v>
       </c>
-      <c r="D11" s="150" t="s">
+      <c r="D11" s="127" t="s">
         <v>273</v>
       </c>
       <c r="E11" s="94" t="s">
@@ -34961,10 +36213,10 @@
       <c r="B12" s="115" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="149">
+      <c r="C12" s="126">
         <v>30</v>
       </c>
-      <c r="D12" s="150" t="s">
+      <c r="D12" s="127" t="s">
         <v>254</v>
       </c>
       <c r="E12" s="95" t="s">
@@ -34978,10 +36230,10 @@
       <c r="B13" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="126">
         <v>30</v>
       </c>
-      <c r="D13" s="150" t="s">
+      <c r="D13" s="127" t="s">
         <v>266</v>
       </c>
       <c r="E13" s="95" t="s">
@@ -35105,7 +36357,7 @@
       <c r="A21" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="151" t="s">
+      <c r="B21" s="128" t="s">
         <v>247</v>
       </c>
       <c r="C21" s="110">

--- a/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
+++ b/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\存档表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAECC81-A4C3-4D4B-8C0C-C493F4007C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1878090-86FD-47F6-B61D-8B6C9C1FCD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="东亚冷站9120一均" sheetId="3" r:id="rId1"/>
-    <sheet name="夜温-40阈值" sheetId="4" r:id="rId2"/>
-    <sheet name="昼温-30阈值" sheetId="8" r:id="rId3"/>
-    <sheet name="连续夜温-40阈值" sheetId="5" r:id="rId4"/>
-    <sheet name="连续昼温-30阈值" sheetId="7" r:id="rId5"/>
+    <sheet name="夜温-50阈值" sheetId="9" r:id="rId2"/>
+    <sheet name="夜温-40阈值" sheetId="4" r:id="rId3"/>
+    <sheet name="昼温-30阈值" sheetId="8" r:id="rId4"/>
+    <sheet name="连续夜温-40阈值" sheetId="5" r:id="rId5"/>
+    <sheet name="连续昼温-30阈值" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="357">
   <si>
     <t>地点</t>
   </si>
@@ -3225,6 +3226,264 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>1966冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1971-1972冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pelly Ranch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯特列尔卡-丘尼亚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Стрелка-Чуня</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大
+育空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1995-1996冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOWER 2S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">单个冬季 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="44"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-50°C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="44"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="44"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天数</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大兴安岭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新疆
+阿勒泰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可可托海水库</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1916-1917</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>托拉赫姆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Тоора-Хем</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂特冈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015-2016冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1998-1999冬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙古
+扎布汗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼伦贝尔乌玛
+黑龙江漠河</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1935-1936</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">冬
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1939-1940</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2022-2023</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌斯季卡连加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Усть-Каренга</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1968-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1969</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="0"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1968-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1969</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Отгон
+&lt;= 19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3236,7 +3495,7 @@
     <numFmt numFmtId="178" formatCode="yyyy\-m"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="86" x14ac:knownFonts="1">
+  <fonts count="98" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3906,6 +4165,101 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="44"/>
+      <color rgb="FF00B0F0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="44"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="44"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF92D050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="28">
     <fill>
@@ -4220,7 +4574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4573,15 +4927,6 @@
     <xf numFmtId="0" fontId="56" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4590,6 +4935,15 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4622,6 +4976,36 @@
     <xf numFmtId="0" fontId="85" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="91" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4630,16 +5014,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFF72585"/>
+      <color rgb="FF4361EE"/>
+      <color rgb="FF3A0CA3"/>
       <color rgb="FF4CC9F0"/>
       <color rgb="FF4895EF"/>
-      <color rgb="FF3F37C9"/>
-      <color rgb="FF480CA8"/>
-      <color rgb="FF3A0CA3"/>
       <color rgb="FF560BAD"/>
       <color rgb="FF7209B7"/>
       <color rgb="FFB5179E"/>
-      <color rgb="FF4361EE"/>
+      <color rgb="FFF72585"/>
+      <color rgb="FF3F37C9"/>
+      <color rgb="FF480CA8"/>
     </mruColors>
   </colors>
   <extLst>
@@ -34714,6 +35098,362 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EF10C5-6C75-43F1-B7AF-F869B6CCA43F}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
+  <cols>
+    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" style="52" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="47" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="139" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="141"/>
+    </row>
+    <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="123"/>
+      <c r="C2" s="124" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="125"/>
+      <c r="E2" s="106" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="57">
+        <v>280</v>
+      </c>
+      <c r="D3" s="90" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="59">
+        <v>84</v>
+      </c>
+      <c r="D4" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="59">
+        <v>83</v>
+      </c>
+      <c r="D5" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="61">
+        <v>44</v>
+      </c>
+      <c r="D6" s="92" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7" s="61">
+        <v>43</v>
+      </c>
+      <c r="D7" s="92" t="s">
+        <v>354</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="78" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="61">
+        <v>41</v>
+      </c>
+      <c r="D8" s="92" t="s">
+        <v>354</v>
+      </c>
+      <c r="E8" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="88"/>
+      <c r="G8" s="87" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="75" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" s="63">
+        <v>35</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>342</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="79" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="63">
+        <v>31</v>
+      </c>
+      <c r="D10" s="94" t="s">
+        <v>354</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="83">
+        <v>24</v>
+      </c>
+      <c r="D11" s="99" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="145" t="s">
+        <v>335</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="83">
+        <v>24</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="55"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="B13" s="146" t="s">
+        <v>343</v>
+      </c>
+      <c r="C13" s="102">
+        <v>19</v>
+      </c>
+      <c r="D13" s="103" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+    </row>
+    <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="147" t="s">
+        <v>348</v>
+      </c>
+      <c r="B14" s="148" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" s="102">
+        <v>19</v>
+      </c>
+      <c r="D14" s="103" t="s">
+        <v>346</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="86" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="69">
+        <v>7</v>
+      </c>
+      <c r="D15" s="144" t="s">
+        <v>350</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" s="142" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="69">
+        <v>4</v>
+      </c>
+      <c r="D16" s="105" t="s">
+        <v>355</v>
+      </c>
+      <c r="E16" s="56"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="97" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="69">
+        <v>3</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="56"/>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="69">
+        <v>3</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>347</v>
+      </c>
+      <c r="E18" s="56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="48" t="s">
+        <v>339</v>
+      </c>
+      <c r="B19" s="143" t="s">
+        <v>349</v>
+      </c>
+      <c r="C19" s="69">
+        <v>3</v>
+      </c>
+      <c r="D19" s="105" t="s">
+        <v>351</v>
+      </c>
+      <c r="E19" s="56"/>
+    </row>
+    <row r="20" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="118" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" s="69">
+        <v>2</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>336</v>
+      </c>
+      <c r="E20" s="56"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E20">
+    <sortCondition descending="1" ref="C3:C20"/>
+    <sortCondition ref="D3:D20"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F386B1A-4DAD-4626-8EB7-CF08CB4064B1}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
@@ -34727,23 +35467,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="120" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="122"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="123" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="120" t="s">
+      <c r="B2" s="123"/>
+      <c r="C2" s="124" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="121"/>
+      <c r="D2" s="125"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -35051,7 +35791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867BCDEB-6279-47D1-8C43-6CA3B2BA5301}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
@@ -35065,23 +35805,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="120" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="122"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="123" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="120" t="s">
+      <c r="B2" s="123"/>
+      <c r="C2" s="124" t="s">
         <v>268</v>
       </c>
-      <c r="D2" s="121"/>
+      <c r="D2" s="125"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -35390,355 +36130,6 @@
       </c>
       <c r="D20" s="105" t="s">
         <v>293</v>
-      </c>
-      <c r="E20" s="56"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E20">
-    <sortCondition descending="1" ref="C3:C20"/>
-  </sortState>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA111638-49D1-45ED-AEC5-4053BA8905D8}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
-  <cols>
-    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
-    <col min="2" max="2" width="20.59765625" style="52" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="47" customWidth="1"/>
-    <col min="4" max="4" width="26.59765625" style="50" customWidth="1"/>
-    <col min="5" max="5" width="23.59765625" style="47" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="47"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
-    </row>
-    <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="122" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="120" t="s">
-        <v>305</v>
-      </c>
-      <c r="D2" s="138"/>
-      <c r="E2" s="106" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="80" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" s="57">
-        <v>303</v>
-      </c>
-      <c r="D3" s="58" t="s">
-        <v>205</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="79" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="78" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="59">
-        <v>118</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="79" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="61">
-        <v>89</v>
-      </c>
-      <c r="D5" s="62" t="s">
-        <v>298</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="79" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="78" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="61">
-        <v>87</v>
-      </c>
-      <c r="D6" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="E6" s="55" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="79" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="63">
-        <v>53</v>
-      </c>
-      <c r="D7" s="64" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="75" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="76" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="65">
-        <v>43</v>
-      </c>
-      <c r="D8" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="65">
-        <v>41</v>
-      </c>
-      <c r="D9" s="66" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="78" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="65">
-        <v>40</v>
-      </c>
-      <c r="D10" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="55" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="79" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="113" t="s">
-        <v>301</v>
-      </c>
-      <c r="C11" s="67">
-        <v>36</v>
-      </c>
-      <c r="D11" s="68" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="75" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="67">
-        <v>35</v>
-      </c>
-      <c r="D12" s="68" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="67">
-        <v>34</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>302</v>
-      </c>
-      <c r="E13" s="56" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="78" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="67">
-        <v>31</v>
-      </c>
-      <c r="D14" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" s="56" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="B15" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="67">
-        <v>30</v>
-      </c>
-      <c r="D15" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="56" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="97" t="s">
-        <v>260</v>
-      </c>
-      <c r="B16" s="53" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="72">
-        <v>27</v>
-      </c>
-      <c r="D16" s="73" t="s">
-        <v>198</v>
-      </c>
-      <c r="E16" s="56"/>
-    </row>
-    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="79" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="72">
-        <v>26</v>
-      </c>
-      <c r="D17" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="E17" s="56" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="72">
-        <v>24</v>
-      </c>
-      <c r="D18" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="E18" s="55"/>
-    </row>
-    <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="76" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="69">
-        <v>7</v>
-      </c>
-      <c r="D19" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="E19" s="55" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="118" t="s">
-        <v>295</v>
-      </c>
-      <c r="B20" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="69">
-        <v>7</v>
-      </c>
-      <c r="D20" s="71" t="s">
-        <v>202</v>
       </c>
       <c r="E20" s="56"/>
     </row>
@@ -35757,6 +36148,355 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA111638-49D1-45ED-AEC5-4053BA8905D8}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
+  <cols>
+    <col min="1" max="1" width="16.59765625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" style="52" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="26.59765625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="23.59765625" style="47" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="120" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="122"/>
+    </row>
+    <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="123"/>
+      <c r="C2" s="124" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" s="138"/>
+      <c r="E2" s="106" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="57">
+        <v>303</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="59">
+        <v>118</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="61">
+        <v>89</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="61">
+        <v>87</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="63">
+        <v>53</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="75" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="65">
+        <v>43</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="65">
+        <v>41</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>300</v>
+      </c>
+      <c r="E9" s="56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="65">
+        <v>40</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="113" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="67">
+        <v>36</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="75" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="67">
+        <v>35</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="67">
+        <v>34</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="79" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="67">
+        <v>31</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="67">
+        <v>30</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="56" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="72">
+        <v>27</v>
+      </c>
+      <c r="D16" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="56"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="B17" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="72">
+        <v>26</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="56" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="72">
+        <v>24</v>
+      </c>
+      <c r="D18" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="E18" s="55"/>
+    </row>
+    <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="69">
+        <v>7</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="55" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="118" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" s="77" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="69">
+        <v>7</v>
+      </c>
+      <c r="D20" s="71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="56"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E20">
+    <sortCondition descending="1" ref="C3:C20"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F0BB6F-5228-4A30-866C-40DE5CC59526}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="24.75" x14ac:dyDescent="0.65"/>
@@ -35770,20 +36510,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="120" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="122"/>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="123" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="122"/>
-      <c r="C2" s="120" t="s">
+      <c r="B2" s="123"/>
+      <c r="C2" s="124" t="s">
         <v>305</v>
       </c>
       <c r="D2" s="138"/>

--- a/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
+++ b/气象/表格文件/存档表格/东亚冷站一均(V1.0).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\存档表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1878090-86FD-47F6-B61D-8B6C9C1FCD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B227F99E-91BB-4896-9A3B-E9298091347C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3480,8 +3480,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Отгон
-&lt;= 19</t>
+    <t>Отгон</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4927,13 +4926,34 @@
     <xf numFmtId="0" fontId="56" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="91" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4973,38 +4993,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="85" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="91" fillId="26" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5256,21 +5255,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="135" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="130"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="137"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -5287,35 +5286,35 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="140" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="133" t="s">
+      <c r="C2" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="131" t="s">
+      <c r="D2" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="131" t="s">
+      <c r="E2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="136" t="s">
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="127"/>
-      <c r="J2" s="126" t="s">
+      <c r="I2" s="134"/>
+      <c r="J2" s="133" t="s">
         <v>127</v>
       </c>
-      <c r="K2" s="127"/>
-      <c r="L2" s="126" t="s">
+      <c r="K2" s="134"/>
+      <c r="L2" s="133" t="s">
         <v>131</v>
       </c>
-      <c r="M2" s="127"/>
+      <c r="M2" s="134"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -5332,13 +5331,13 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="134"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="139"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="139"/>
+      <c r="G3" s="139"/>
       <c r="H3" s="14" t="s">
         <v>11</v>
       </c>
@@ -35111,23 +35110,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="127" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="141"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="129"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="131" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="125"/>
+      <c r="D2" s="132"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -35290,7 +35289,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="123" t="s">
         <v>335</v>
       </c>
       <c r="B12" s="76" t="s">
@@ -35312,7 +35311,7 @@
       <c r="A13" s="79" t="s">
         <v>261</v>
       </c>
-      <c r="B13" s="146" t="s">
+      <c r="B13" s="124" t="s">
         <v>343</v>
       </c>
       <c r="C13" s="102">
@@ -35328,10 +35327,10 @@
       <c r="G13" s="87"/>
     </row>
     <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="125" t="s">
         <v>348</v>
       </c>
-      <c r="B14" s="148" t="s">
+      <c r="B14" s="126" t="s">
         <v>345</v>
       </c>
       <c r="C14" s="102">
@@ -35354,7 +35353,7 @@
       <c r="C15" s="69">
         <v>7</v>
       </c>
-      <c r="D15" s="144" t="s">
+      <c r="D15" s="122" t="s">
         <v>350</v>
       </c>
       <c r="E15" s="56" t="s">
@@ -35365,7 +35364,7 @@
       <c r="A16" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="120" t="s">
         <v>203</v>
       </c>
       <c r="C16" s="69">
@@ -35412,7 +35411,7 @@
       <c r="A19" s="48" t="s">
         <v>339</v>
       </c>
-      <c r="B19" s="143" t="s">
+      <c r="B19" s="121" t="s">
         <v>349</v>
       </c>
       <c r="C19" s="69">
@@ -35467,23 +35466,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="145" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="131" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="125"/>
+      <c r="D2" s="132"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -35805,23 +35804,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="145" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="131" t="s">
         <v>268</v>
       </c>
-      <c r="D2" s="125"/>
+      <c r="D2" s="132"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -36161,23 +36160,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="145" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="131" t="s">
         <v>305</v>
       </c>
-      <c r="D2" s="138"/>
+      <c r="D2" s="148"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
@@ -36510,23 +36509,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="76.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="145" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="122"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="147"/>
     </row>
     <row r="2" spans="1:5" ht="44" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="130"/>
+      <c r="C2" s="131" t="s">
         <v>305</v>
       </c>
-      <c r="D2" s="138"/>
+      <c r="D2" s="148"/>
       <c r="E2" s="106" t="s">
         <v>177</v>
       </c>
